--- a/modules/conjoint/docs/Conjoint_Config_Template.xlsx
+++ b/modules/conjoint/docs/Conjoint_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <si>
     <t xml:space="preserve">TURAS Conjoint Analysis Configuration</t>
   </si>
@@ -662,6 +662,42 @@
   </si>
   <si>
     <t xml:space="preserve">Alchemer score column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATS PACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generate_stats_pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
   </si>
   <si>
     <t xml:space="preserve">Conjoint Attribute Definitions</t>
@@ -2533,8 +2569,94 @@
         <v>205</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
@@ -2553,6 +2675,8 @@
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A83:E83"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
@@ -2570,7 +2694,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="18">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="19">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"generic,alchemer"</xm:f>
@@ -2679,6 +2803,12 @@
           </x14:formula1>
           <xm:sqref>B76:B76</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B82:B82</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -2697,89 +2827,89 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2855,34 +2985,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>14</v>
@@ -2974,40 +3104,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
@@ -3153,12 +3283,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3177,7 +3307,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2">
@@ -3187,27 +3317,27 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
@@ -3217,37 +3347,37 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16">
@@ -3257,32 +3387,32 @@
     </row>
     <row r="17">
       <c r="A17" s="14" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23">
@@ -3297,12 +3427,12 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27">
@@ -3312,12 +3442,12 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
